--- a/WebDataWorld/LabDatabase/static/LabDatabase/DownloadFile/AssemblyPlan.xlsx
+++ b/WebDataWorld/LabDatabase/static/LabDatabase/DownloadFile/AssemblyPlan.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\WebDatabase\WebDataWorld\LabDatabase\static\LabDatabase\DownloadFile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87D693DE-3F03-4804-A2AD-7CFCC6DFB197}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D26ED715-BA30-42B1-82B9-87EC471C4A08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="13020" windowHeight="12360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5040" yWindow="5115" windowWidth="17265" windowHeight="9570" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Part</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -44,6 +44,22 @@
   </si>
   <si>
     <t>Note</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Alias</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Level</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Part Start Scar</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Part End Scar</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -369,26 +385,42 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="15.75" customWidth="1"/>
+    <col min="1" max="4" width="15.75" customWidth="1"/>
+    <col min="5" max="6" width="12.25" customWidth="1"/>
+    <col min="7" max="7" width="13.375" customWidth="1"/>
+    <col min="8" max="8" width="17.125" customWidth="1"/>
+    <col min="9" max="9" width="13.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>3</v>
       </c>
       <c r="B1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" t="s">
+      <c r="F1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
+      <c r="H1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" t="s">
+      <c r="I1" t="s">
         <v>4</v>
       </c>
     </row>
